--- a/frontend/public/gddp.xlsx
+++ b/frontend/public/gddp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website\MITRA-Website-V1\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website\MahaMitra\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AFBC3F-D70F-48B5-9CAC-1C55F4049B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9CC3A9-F904-4BF8-909D-72066C288085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2011-12" sheetId="1" r:id="rId1"/>
